--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486468_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486468_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.8088</v>
+        <v>7.934</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2782</v>
+        <v>5.4959</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5305</v>
+        <v>2.4381</v>
       </c>
       <c r="G2" t="n">
         <v>3.9249</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6664</v>
+        <v>0.7916</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1476</v>
+        <v>0.3653</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5188</v>
+        <v>0.4263</v>
       </c>
       <c r="V2" t="n">
         <v>1.695</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Y. BARRUETA</t>
+          <t>A. GALAN POZO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1359</v>
+        <v>7.3244</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7716</v>
+        <v>4.0156</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3643</v>
+        <v>3.3088</v>
       </c>
       <c r="G3" t="n">
-        <v>5.442</v>
+        <v>5.9801</v>
       </c>
       <c r="H3" t="n">
-        <v>3.0626</v>
+        <v>3.2238</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3794</v>
+        <v>2.7563</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8707</v>
+        <v>4.6837</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1534</v>
+        <v>1.7186</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7173</v>
+        <v>2.9651</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5713</v>
+        <v>1.2964</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9091</v>
+        <v>1.5052</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3379</v>
+        <v>-0.2088</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8462</v>
+        <v>1.6043</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3581</v>
+        <v>0.4194</v>
       </c>
       <c r="U3" t="n">
-        <v>1.488</v>
+        <v>1.1849</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3698</v>
+        <v>-1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GALAN POZO</t>
+          <t>Y. BARRUETA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.9207</v>
+        <v>7.2554</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6118</v>
+        <v>4.1068</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3088</v>
+        <v>3.1486</v>
       </c>
       <c r="G4" t="n">
-        <v>5.9801</v>
+        <v>5.442</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2238</v>
+        <v>3.0626</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7563</v>
+        <v>2.3794</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6837</v>
+        <v>4.8707</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7186</v>
+        <v>2.1534</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9651</v>
+        <v>2.7173</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2964</v>
+        <v>0.5713</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5052</v>
+        <v>0.9091</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2088</v>
+        <v>-0.3379</v>
       </c>
       <c r="P4" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2005</v>
+        <v>1.9657</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0156</v>
+        <v>0.6934</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1849</v>
+        <v>1.2723</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.13</v>
+        <v>-0.3698</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.7658</v>
+        <v>7.1388</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9211</v>
+        <v>3.3249</v>
       </c>
       <c r="F5" t="n">
-        <v>3.8447</v>
+        <v>3.8139</v>
       </c>
       <c r="G5" t="n">
         <v>4.6252</v>
@@ -844,13 +844,13 @@
         <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2297</v>
+        <v>0.1433</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.2812</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4553</v>
+        <v>0.4245</v>
       </c>
       <c r="V5" t="n">
         <v>0.1952</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.8744</v>
+        <v>6.0749</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9291</v>
+        <v>1.3761</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9453</v>
+        <v>4.6987</v>
       </c>
       <c r="G6" t="n">
         <v>2.8724</v>
@@ -922,13 +922,13 @@
         <v>2.6101</v>
       </c>
       <c r="S6" t="n">
-        <v>0.392</v>
+        <v>0.5924</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.262</v>
+        <v>0.1851</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6539</v>
+        <v>0.4074</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>5.5349</v>
+        <v>4.6679</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1563</v>
+        <v>2.5975</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3786</v>
+        <v>2.0704</v>
       </c>
       <c r="G7" t="n">
         <v>2.5812</v>
@@ -1000,13 +1000,13 @@
         <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>2.151</v>
+        <v>1.284</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2846</v>
+        <v>0.7258</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.5582</v>
       </c>
       <c r="V7" t="n">
         <v>1.8902</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.8091</v>
+        <v>4.5952</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8448</v>
+        <v>2.2918</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9643</v>
+        <v>2.3034</v>
       </c>
       <c r="G8" t="n">
         <v>2.8741</v>
@@ -1078,13 +1078,13 @@
         <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5875</v>
+        <v>0.1986</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.411</v>
+        <v>0.0361</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1765</v>
+        <v>0.1625</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>A. GRELA ROJAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5699</v>
+        <v>2.5499</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5111</v>
+        <v>0.8884</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0588</v>
+        <v>1.6615</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3536</v>
+        <v>2.7653</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2588</v>
+        <v>1.1405</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0948</v>
+        <v>1.6248</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2376</v>
+        <v>2.1382</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3523</v>
+        <v>0.876</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1147</v>
+        <v>1.2622</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.6271</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6111</v>
+        <v>0.2645</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0199</v>
+        <v>0.3626</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2175</v>
+        <v>-0.435</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4338</v>
+        <v>0.2196</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8362</v>
+        <v>-0.1622</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5976</v>
+        <v>0.3818</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GRELA ROJAS</t>
+          <t>A. ETXEGUREN GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.5306</v>
+        <v>1.9875</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.548</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7539</v>
+        <v>1.4396</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7653</v>
+        <v>1.4186</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1405</v>
+        <v>1.688</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6248</v>
+        <v>-0.2694</v>
       </c>
       <c r="J10" t="n">
-        <v>2.1382</v>
+        <v>0.6489</v>
       </c>
       <c r="K10" t="n">
-        <v>0.876</v>
+        <v>0.4959</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2622</v>
+        <v>0.153</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6271</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2645</v>
+        <v>1.1921</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3626</v>
+        <v>-0.4224</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2003</v>
+        <v>0.1763</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.274</v>
+        <v>-0.1009</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4743</v>
+        <v>0.2773</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ETXEGUREN GONZALEZ</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2.0887</v>
+        <v>1.5448</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9265</v>
+        <v>-0.6065</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1622</v>
+        <v>2.1513</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4186</v>
+        <v>0.3536</v>
       </c>
       <c r="H11" t="n">
-        <v>1.688</v>
+        <v>0.2588</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2694</v>
+        <v>0.0948</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6489</v>
+        <v>-0.2376</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4959</v>
+        <v>-0.3523</v>
       </c>
       <c r="L11" t="n">
-        <v>0.153</v>
+        <v>0.1147</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1921</v>
+        <v>0.6111</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4224</v>
+        <v>-0.0199</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5225</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2775</v>
+        <v>1.4087</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2776</v>
+        <v>0.7186</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0001</v>
+        <v>0.6901</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1441</v>
+        <v>0.5486</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.637</v>
+        <v>-1.345</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4929</v>
+        <v>1.8936</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3033</v>
@@ -1390,13 +1390,13 @@
         <v>1.5225</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6817</v>
+        <v>1.3744</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1526</v>
+        <v>0.4446</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5291</v>
+        <v>0.9298</v>
       </c>
       <c r="V12" t="n">
         <v>1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.1016</v>
+        <v>-0.3741</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8394</v>
+        <v>-1.9886</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7377</v>
+        <v>1.6145</v>
       </c>
       <c r="G13" t="n">
         <v>-0.029</v>
@@ -1468,13 +1468,13 @@
         <v>0.6525</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6028</v>
+        <v>1.3303</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6044</v>
+        <v>0.2464</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2072</v>
+        <v>1.0839</v>
       </c>
       <c r="V13" t="n">
         <v>0.9347</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>50.7931</v>
+        <v>51.2473</v>
       </c>
       <c r="E14" t="n">
-        <v>20.2508</v>
+        <v>20.70489999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>30.542</v>
+        <v>30.5424</v>
       </c>
       <c r="G14" t="n">
         <v>31.5051</v>
@@ -1516,7 +1516,7 @@
         <v>25.8674</v>
       </c>
       <c r="I14" t="n">
-        <v>5.6378</v>
+        <v>5.637800000000001</v>
       </c>
       <c r="J14" t="n">
         <v>22.577</v>
@@ -1534,7 +1534,7 @@
         <v>13.8966</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.9686</v>
+        <v>-4.968599999999999</v>
       </c>
       <c r="P14" t="n">
         <v>5.437600000000001</v>
@@ -1546,13 +1546,13 @@
         <v>17.4003</v>
       </c>
       <c r="S14" t="n">
-        <v>10.635</v>
+        <v>11.0892</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8359</v>
+        <v>3.2904</v>
       </c>
       <c r="U14" t="n">
-        <v>7.798900000000001</v>
+        <v>7.799</v>
       </c>
       <c r="V14" t="n">
         <v>3.2153</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1387</v>
+        <v>1.6994</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6603</v>
+        <v>2.4368</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>2.039</v>
@@ -1624,13 +1624,13 @@
         <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1422</v>
+        <v>-0.2971</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2139</v>
+        <v>-0.4374</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3561</v>
+        <v>0.1403</v>
       </c>
       <c r="V15" t="n">
         <v>-1.13</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2314</v>
+        <v>0.1274</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2443</v>
+        <v>-0.1325</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4757</v>
+        <v>0.2599</v>
       </c>
       <c r="G16" t="n">
         <v>0.6853</v>
@@ -1702,13 +1702,13 @@
         <v>0.435</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1986</v>
+        <v>0.0946</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3425</v>
+        <v>-0.2307</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5411</v>
+        <v>0.3254</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GARUBA ALARI</t>
+          <t>A. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9117</v>
+        <v>-1.779</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.9709</v>
+        <v>-1.5198</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0592</v>
+        <v>-0.2592</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1922</v>
+        <v>-0.7005</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0432</v>
+        <v>0.0486</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.149</v>
+        <v>-0.749</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7069</v>
+        <v>-0.1331</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7268</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0199</v>
+        <v>-0.1331</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4854</v>
+        <v>-0.5674</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3164</v>
+        <v>0.0486</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1689</v>
+        <v>-0.616</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5225</v>
+        <v>-0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3926</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4333</v>
+        <v>-0.2085</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1286</v>
+        <v>-0.2992</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3047</v>
+        <v>0.0907</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. HARGUINDEY MANEIRO</t>
+          <t>A. MARTIN MARIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9781</v>
+        <v>-1.9121</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6316</v>
+        <v>-0.1115</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3465</v>
+        <v>-1.8006</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7005</v>
+        <v>1.369</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0486</v>
+        <v>0.0789</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.749</v>
+        <v>1.2901</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1331</v>
+        <v>2.1597</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.1492</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1331</v>
+        <v>2.0105</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5674</v>
+        <v>-0.7907</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0486</v>
+        <v>-0.0703</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.616</v>
+        <v>-0.7204</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4076</v>
+        <v>-1.2386</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.411</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0034</v>
+        <v>-0.2725</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4477</v>
+        <v>-2.1754</v>
       </c>
       <c r="E19" t="n">
         <v>-0.0411</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4066</v>
+        <v>-2.1343</v>
       </c>
       <c r="G19" t="n">
         <v>-2.3382</v>
@@ -1936,13 +1936,13 @@
         <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7398</v>
+        <v>-0.4675</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0769</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6629</v>
+        <v>-0.3906</v>
       </c>
       <c r="V19" t="n">
         <v>0.1952</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. RIVERA CARROLL</t>
+          <t>A. GARUBA ALARI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7145</v>
+        <v>-2.2585</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2167</v>
+        <v>-3.1944</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9312</v>
+        <v>0.9359</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.423</v>
+        <v>-1.1922</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7186</v>
+        <v>-1.0432</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7044</v>
+        <v>-0.149</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0731</v>
+        <v>-0.7069</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4412</v>
+        <v>-0.7268</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6319</v>
+        <v>0.0199</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.4961</v>
+        <v>-0.4854</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.1598</v>
+        <v>-0.3164</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3364</v>
+        <v>-0.1689</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2262</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8989</v>
+        <v>-0.0949</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3274</v>
+        <v>0.1815</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9347</v>
+        <v>0.3698</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1952</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MARTIN MARIN</t>
+          <t>I. RIVERA CARROLL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7611</v>
+        <v>-2.9123</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4468</v>
+        <v>-0.0069</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3143</v>
+        <v>-2.9054</v>
       </c>
       <c r="G21" t="n">
-        <v>1.369</v>
+        <v>-2.423</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0789</v>
+        <v>-1.7186</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2901</v>
+        <v>-0.7044</v>
       </c>
       <c r="J21" t="n">
-        <v>2.1597</v>
+        <v>1.0731</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1492</v>
+        <v>0.4412</v>
       </c>
       <c r="L21" t="n">
-        <v>2.0105</v>
+        <v>0.6319</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7907</v>
+        <v>-3.4961</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0703</v>
+        <v>-2.1598</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7204</v>
+        <v>-1.3364</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.0877</v>
+        <v>-1.424</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3014</v>
+        <v>-1.1224</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7863</v>
+        <v>-0.3016</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.2599</v>
+        <v>0.9347</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.2599</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7604</v>
+        <v>-4.1818</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9545</v>
+        <v>-2.4015</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.806</v>
+        <v>-1.7802</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8664</v>
@@ -2170,13 +2170,13 @@
         <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8717</v>
+        <v>-1.293</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6249</v>
+        <v>-1.0719</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2468</v>
+        <v>-0.2211</v>
       </c>
       <c r="V22" t="n">
         <v>0.7602</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.5549</v>
+        <v>-7.1607</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5622</v>
+        <v>-5.8975</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9927</v>
+        <v>-1.2631</v>
       </c>
       <c r="G23" t="n">
         <v>-6.216</v>
@@ -2248,13 +2248,13 @@
         <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.1013</v>
+        <v>-1.707</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9673</v>
+        <v>-1.3026</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1339</v>
+        <v>-0.4044</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7602</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.6116</v>
+        <v>-7.3393</v>
       </c>
       <c r="E24" t="n">
         <v>-4.1308</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.4808</v>
+        <v>-3.2085</v>
       </c>
       <c r="G24" t="n">
         <v>-5.6082</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8083</v>
+        <v>-0.536</v>
       </c>
       <c r="T24" t="n">
         <v>-0.1454</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6629</v>
+        <v>-0.3906</v>
       </c>
       <c r="V24" t="n">
         <v>-0.7602</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.6386</v>
+        <v>-10.2891</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.3294</v>
+        <v>-7.8824</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3091</v>
+        <v>-2.4067</v>
       </c>
       <c r="G25" t="n">
         <v>-7.7906</v>
@@ -2404,13 +2404,13 @@
         <v>1.305</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.413</v>
+        <v>-1.0635</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.6439</v>
+        <v>-1.1969</v>
       </c>
       <c r="U25" t="n">
-        <v>0.231</v>
+        <v>0.1334</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5649999999999999</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.7844</v>
+        <v>-11.1216</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.477499999999999</v>
+        <v>-8.0305</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.3069</v>
+        <v>-3.0912</v>
       </c>
       <c r="G26" t="n">
         <v>-5.4631</v>
@@ -2482,13 +2482,13 @@
         <v>0.87</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.7536</v>
+        <v>-1.0908</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.3014</v>
+        <v>-0.8544</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4522</v>
+        <v>-0.2364</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-50.7929</v>
+        <v>-49.303</v>
       </c>
       <c r="E27" t="n">
         <v>-30.9121</v>
       </c>
       <c r="F27" t="n">
-        <v>-19.8809</v>
+        <v>-18.3908</v>
       </c>
       <c r="G27" t="n">
         <v>-31.5049</v>
@@ -2560,13 +2560,13 @@
         <v>11.9626</v>
       </c>
       <c r="S27" t="n">
-        <v>-10.6351</v>
+        <v>-9.144899999999998</v>
       </c>
       <c r="T27" t="n">
         <v>-7.798900000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.8361</v>
+        <v>-1.3459</v>
       </c>
       <c r="V27" t="n">
         <v>-3.2154</v>
